--- a/Configuracion/DatosParaCorreos.xlsx
+++ b/Configuracion/DatosParaCorreos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\uipath\RIBA24GMXcmx01_Endosos\Configuracion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85226F49-808B-4BD7-A773-D2DC596AAA15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF69C79E-3C56-46E1-9034-087402B0D5F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="55">
   <si>
     <t>Nombre</t>
   </si>
@@ -196,6 +196,15 @@
   </si>
   <si>
     <t>andres.minero@inbusiness.tech;luis.galeote@GMX.COM.MX;victor.ramirez@GMX.COM.MX</t>
+  </si>
+  <si>
+    <t>areli.arreola@GMX.COM.MX;suscripciontecnicadigital@gmx.com.mx;luis.galeote@GMX.COM.MX;victor.ramirez@GMX.COM.MX;andres.minero@inbusiness.tech</t>
+  </si>
+  <si>
+    <t>andres.minero@inbusiness.tech;victor.ramirez@GMX.COM.MX;luis.galeote@GMX.COM.MX</t>
+  </si>
+  <si>
+    <t>andres.minero@inbusiness.tech</t>
   </si>
 </sst>
 </file>
@@ -616,15 +625,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:Z26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="46.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="46.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="150.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="46.33203125" style="2"/>
+    <col min="1" max="1" width="45.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="150.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="46.28515625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -658,7 +667,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -669,13 +678,13 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:26" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C3" s="7"/>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -686,7 +695,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -697,7 +706,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -709,7 +718,7 @@
       </c>
       <c r="D6" s="5"/>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
@@ -720,7 +729,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
@@ -731,13 +740,13 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:26" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:26" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C9" s="7"/>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>20</v>
       </c>
@@ -746,7 +755,7 @@
       </c>
       <c r="C10" s="4"/>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>23</v>
       </c>
@@ -757,7 +766,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>24</v>
       </c>
@@ -765,7 +774,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>25</v>
       </c>
@@ -773,7 +782,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>26</v>
       </c>
@@ -784,7 +793,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:26" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>27</v>
       </c>
@@ -795,13 +804,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:26" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>32</v>
       </c>
       <c r="C16" s="7"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>33</v>
       </c>
@@ -810,12 +819,12 @@
       </c>
       <c r="C17" s="4"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="12" t="s">
-        <v>51</v>
+      <c r="B18" t="s">
+        <v>53</v>
       </c>
       <c r="C18" t="s">
         <v>51</v>
@@ -824,29 +833,35 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>34</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D19" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B20" t="s">
-        <v>43</v>
+      <c r="B20" s="12" t="s">
+        <v>54</v>
       </c>
       <c r="C20" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D20" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>36</v>
       </c>
@@ -854,7 +869,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>49</v>
       </c>
@@ -862,7 +877,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>37</v>
       </c>
@@ -873,7 +888,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="165" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
         <v>38</v>
       </c>
@@ -884,7 +899,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>29</v>
       </c>
@@ -892,7 +907,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B26" s="10"/>
     </row>
   </sheetData>
